--- a/AI Audit Log_NguyenThiThuyTien.xlsx
+++ b/AI Audit Log_NguyenThiThuyTien.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nguyenthithuytien/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nguyenthithuytien/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FD8D86-5B7C-9D40-BFFA-4AB9A8825EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755D849E-2EDF-1A40-B8AF-D0072DC3A186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="660" windowWidth="28480" windowHeight="15820" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="160" yWindow="660" windowWidth="28480" windowHeight="15820" activeTab="1" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Template" sheetId="1" r:id="rId1"/>
-    <sheet name="Assignment 1" sheetId="2" r:id="rId2"/>
+    <sheet name="Week 2" sheetId="1" r:id="rId1"/>
+    <sheet name="Week 3" sheetId="2" r:id="rId2"/>
     <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
     <sheet name="Assignment 3" sheetId="4" r:id="rId4"/>
   </sheets>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -381,6 +381,434 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Tôi đổi lại một số tên use case để thống nhất cách đặt tên và dễ hiểu hơn khi trình bày.</t>
+    </r>
+  </si>
+  <si>
+    <t>Slot 5</t>
+  </si>
+  <si>
+    <t>“Trong hệ thống quản lý thư viện online, nên xác định các Entity chính như thế nào để tránh thiếu class khi vẽ UML?”</t>
+  </si>
+  <si>
+    <t>“Ở giai đoạn phân tích hệ thống, có cần thêm DAO hoặc Repository vào Class Diagram không?”</t>
+  </si>
+  <si>
+    <t>“Nên biểu diễn Interface trong UML như thế nào để đúng chuẩn?”</t>
+  </si>
+  <si>
+    <t>“Sequence Diagram có cần hiển thị đầy đủ Database hay không?”</t>
+  </si>
+  <si>
+    <t>“Khi nào nên dùng Activity Diagram thay vì Sequence Diagram?”</t>
+  </si>
+  <si>
+    <t>“Trong Use Case Diagram, chức năng Login nên include hay extend với Register?”</t>
+  </si>
+  <si>
+    <t>“Có nên đưa Validation vào Sequence Diagram không?”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất các Entity cốt lõi gồm: Book, Author, Member, BorrowTicket, Librarian và Category. Đồng thời giải thích rằng Entity nên đại diện cho dữ liệu tồn tại lâu dài trong hệ thống.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Người học bổ sung thêm Reservation vì hệ thống có chức năng giữ sách trước.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>“Trong UML, multiplicity 0..</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 1..</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, và 1 khác nhau như thế nào?”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nghĩa là bắt buộc đúng một đối tượng; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>0..*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là có thể không có hoặc có nhiều; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>1..*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là phải có ít nhất một. AI cũng đưa ví dụ thực tế giữa Customer và Order.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Người học điều chỉnh multiplicity của Customer – Order từ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> thành </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>0..*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để phù hợp nghiệp vụ khách chưa mua hàng vẫn có tài khoản.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI cho rằng nếu sơ đồ phục vụ phân tích nghiệp vụ thì chỉ nên tập trung vào Entity và quan hệ nghiệp vụ. DAO/Repository phù hợp hơn ở giai đoạn thiết kế chi tiết.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Người học giữ sơ đồ đơn giản ở mức domain model và để Repository sang sơ đồ thiết kế sau.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI hướng dẫn rằng Interface có thể dùng ký hiệu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;&lt;interface&gt;&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hoặc hình tròn lollipop. Quan hệ triển khai dùng nét đứt với mũi tên tam giác rỗng.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Người học áp dụng Interface cho PaymentService và EmailService để tăng tính mở rộng cho hệ thống.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích rằng Sequence Diagram chủ yếu mô tả luồng tương tác giữa actor và object. Database chỉ nên thêm nếu cần làm rõ quá trình truy vấn dữ liệu.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Người học chỉ giữ Repository thay vì vẽ trực tiếp Database để sơ đồ gọn hơn.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI phân tích rằng Activity Diagram phù hợp mô tả luồng nghiệp vụ tổng quát, còn Sequence Diagram tập trung vào thứ tự gọi hàm giữa các object.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Dùng Activity Diagram cho quy trình đặt vé và Sequence Diagram cho chức năng thanh toán.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI cho biết Login và Register là hai use case độc lập nên không cần include hoặc extend. Chỉ nên liên kết trực tiếp với Actor.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Người học tách riêng hai use case để tránh hiểu sai quan hệ chức năng.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất chỉ nên thể hiện các bước validation quan trọng ảnh hưởng đến luồng xử lý chính, ví dụ kiểm tra dữ liệu rỗng hoặc xác thực tài khoản.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Người học thêm bước validate login trước khi gọi AuthService để luồng xử lý thực tế hơn.</t>
     </r>
   </si>
 </sst>
@@ -388,7 +816,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -423,6 +851,30 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -461,7 +913,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -486,6 +938,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -951,9 +1415,233 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E3EFE9-6FFB-49CC-BE69-0C0E36C6253E}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" style="10"/>
+    <col min="2" max="2" width="31.33203125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="42.6640625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="52.6640625" style="9" customWidth="1"/>
+    <col min="5" max="16384" width="8.83203125" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="12">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="12">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="12">
+        <v>3</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="12">
+        <v>4</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="12">
+        <v>5</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="31" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="47" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="12">
+        <v>6</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="12">
+        <v>7</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="A16" s="12">
+        <v>8</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/AI Audit Log_NguyenThiThuyTien.xlsx
+++ b/AI Audit Log_NguyenThiThuyTien.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nguyenthithuytien/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nguyenthithuytien/Documents/swd392/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755D849E-2EDF-1A40-B8AF-D0072DC3A186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A209CFB7-9D7A-3E4E-87CB-92E6782D4B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="660" windowWidth="28480" windowHeight="15820" activeTab="1" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="160" yWindow="660" windowWidth="28480" windowHeight="15820" activeTab="2" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 2" sheetId="1" r:id="rId1"/>
     <sheet name="Week 3" sheetId="2" r:id="rId2"/>
-    <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 4" sheetId="3" r:id="rId3"/>
+    <sheet name="Week 5" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 6" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="93">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -809,6 +810,1081 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Người học thêm bước validate login trước khi gọi AuthService để luồng xử lý thực tế hơn.</t>
+    </r>
+  </si>
+  <si>
+    <t>Slot 7</t>
+  </si>
+  <si>
+    <t>Slot 9</t>
+  </si>
+  <si>
+    <t>Slot 11</t>
+  </si>
+  <si>
+    <t>"Trong Class Diagram của hệ thống Authentication, nên biểu diễn quan hệ giữa User Entity, AuthenticationService và JWTService như thế nào?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI phân tích rằng AuthenticationService đóng vai trò trung gian xử lý nghiệp vụ đăng nhập, trong khi JWTService chỉ cung cấp chức năng tạo và xác thực token. Quan hệ phù hợp là Dependency từ AuthenticationService đến JWTService thay vì Association trực tiếp với User. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi cập nhật Class Diagram để tách rõ trách nhiệm giữa AuthenticationService và JWTService, giúp giảm sự phụ thuộc không cần thiết giữa Entity và các lớp xử lý bảo mật.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Trong thiết kế hệ thống, quan hệ giữa Service Layer và Repository Layer nên được thể hiện bằng Association hay Dependency trong UML?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích rằng Service chỉ sử dụng Repository để truy xuất dữ liệu, không sở hữu Repository, nên Dependency là cách biểu diễn phù hợp hơn. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi thay đổi quan hệ giữa Service và Repository thành Dependency để phản ánh đúng nguyên tắc phân tầng trong kiến trúc Backend.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Có nên đưa Database Entity và Domain Model thành hai lớp riêng biệt trong Class Diagram không? Hãy phân tích ưu nhược điểm."</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích rằng việc tách Entity và Domain Model giúp giảm coupling với Database và phù hợp với Domain Driven Design, nhưng làm tăng số lượng class cần quản lý. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi giữ Entity riêng biệt với Business Model trong thiết kế để dễ dàng thay đổi cấu trúc database mà không ảnh hưởng logic nghiệp vụ.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Cách biểu diễn Generic Class hoặc Template Class (ví dụ Repository) trong UML Class Diagram như thế nào?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI hướng dẫn sử dụng ký hiệu Generic bằng cách đặt kiểu dữ liệu trong dấu ngoặc nhọn, ví dụ Repository&lt;User&gt;. Điều này thể hiện khả năng tái sử dụng cùng một Repository cho nhiều Entity khác nhau. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi sử dụng Generic Repository trong Class Diagram để giảm sự lặp lại code và thể hiện khả năng mở rộng của kiến trúc.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Đánh giá việc Controller gọi trực tiếp nhiều Service trong Class Diagram. Điều này có gây vấn đề về thiết kế không?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI nhận xét rằng Controller phụ thuộc quá nhiều Service có thể vi phạm nguyên tắc Single Responsibility Principle. AI đề xuất sử dụng Facade hoặc Application Service để gom các xử lý phức tạp. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi điều chỉnh thiết kế bằng cách giảm số lượng dependency trực tiếp từ Controller và chuyển một số logic điều phối sang lớp trung gian.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Trong UML Class Diagram, nên thể hiện các lớp Middleware như AuthenticationMiddleware, LoggingMiddleware hay không?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích Middleware thuộc tầng xử lý request nên chỉ cần thể hiện khi nó tham gia trực tiếp vào luồng nghiệp vụ hoặc có ảnh hưởng kiến trúc quan trọng. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi không đưa toàn bộ Middleware vào Class Diagram tổng thể để tránh làm biểu đồ quá phức tạp, chỉ ghi chú ở phần kiến trúc hệ thống.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Phân tích việc sử dụng Singleton Pattern cho các Service trong Backend. Có nên thể hiện Pattern này trong Class Diagram không?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích Singleton có thể biểu diễn bằng stereotype hoặc ghi chú UML, nhưng không nên lạm dụng vì Dependency Injection hiện đại đã quản lý vòng đời object tốt hơn. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi không sử dụng Singleton trực tiếp trong Class Diagram mà để Framework quản lý dependency injection nhằm đảm bảo tính linh hoạt.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Các lớp Validation như UserValidator, OrderValidator có nên xuất hiện trong Class Diagram chính của hệ thống không?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI cho rằng Validation Layer chỉ nên được thể hiện nếu nó chứa các rule nghiệp vụ quan trọng. Các validation đơn giản có thể bỏ qua để tránh làm biểu đồ khó đọc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi chỉ đưa các Validator quan trọng liên quan đến nghiệp vụ vào Class Diagram, còn validation cơ bản được xử lý trong code nhưng không thể hiện trên sơ đồ.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Phân tích Sequence Diagram cho chức năng tạo đơn hàng (Create Order), bao gồm các thành phần Client, OrderController, OrderService, OrderRepository và Database."</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI mô tả luồng xử lý tuần tự: Client gửi request tạo đơn, Controller tiếp nhận dữ liệu, Service kiểm tra nghiệp vụ, Repository lưu thông tin Order và trả kết quả về Client. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi sử dụng cấu trúc Sequence Diagram này làm mẫu cho các chức năng nghiệp vụ có nhiều tầng xử lý trong hệ thống.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Trong Sequence Diagram, cách biểu diễn vòng lặp xử lý danh sách dữ liệu (ví dụ: thêm nhiều sản phẩm vào giỏ hàng) bằng fragment nào?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích sử dụng fragment </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>loop</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trong UML để thể hiện hành động được lặp lại theo điều kiện hoặc số lượng phần tử trong danh sách. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi bổ sung khối </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>loop</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vào Sequence Diagram của chức năng Cart để mô tả rõ quá trình xử lý từng Item trong danh sách sản phẩm.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Hướng dẫn cách thể hiện xử lý lỗi trong Sequence Diagram khi Service phát sinh Exception và trả lỗi về Controller."</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất sử dụng fragment </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>alt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hoặc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>opt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để biểu diễn nhánh xử lý thành công và thất bại. Exception có thể được mô tả bằng message trả về từ Service tới Controller. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi cập nhật Sequence Diagram bằng cách thêm nhánh Error Handling để thể hiện rõ các trường hợp lỗi Validation hoặc Database Failure.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Phân tích cách biểu diễn bất đồng bộ (Asynchronous Call) trong Sequence Diagram khi hệ thống gửi email hoặc xử lý background job."</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích rằng các tác vụ không cần chờ kết quả trả về nên sử dụng mũi tên bất đồng bộ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>-&gt;&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trong UML. Ví dụ: UserService gọi EmailService gửi OTP nhưng không cần giữ request quá lâu. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi sử dụng Asynchronous Message cho các chức năng gửi email, notification nhằm phản ánh đúng kiến trúc xử lý thực tế.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Vẽ Sequence Diagram cho chức năng thanh toán online với PaymentService và hệ thống bên thứ ba như VNPay/PayPal. Cần thể hiện callback như thế nào?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI hướng dẫn tạo thêm lifeline External Payment Gateway và sử dụng message callback từ hệ thống thanh toán quay lại Backend sau khi giao dịch hoàn tất. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi thêm External System vào Sequence Diagram để phân biệt rõ các thành phần nội bộ và dịch vụ bên ngoài.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Cách biểu diễn trạng thái khởi tạo (Initial State) và trạng thái kết thúc (Final State) trong State Diagram như thế nào?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích rằng Initial State được biểu diễn bằng hình tròn đen, thể hiện điểm bắt đầu của vòng đời object. Final State được biểu diễn bằng hình tròn kép, thể hiện trạng thái kết thúc và object không còn tiếp tục chuyển đổi. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi bổ sung Initial và Final State vào các State Diagram quan trọng như Order Lifecycle để thể hiện rõ điểm bắt đầu và kết thúc của quy trình nghiệp vụ.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Có nên sử dụng Composite State trong State Diagram không? Composite State được áp dụng trong trường hợp nào?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích Composite State dùng để gom nhóm nhiều state con có liên quan thành một state lớn hơn, giúp quản lý các lifecycle phức tạp. Ví dụ Payment có thể chứa các state Processing, Verifying và Completed. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi sử dụng Composite State cho những object có nhiều bước xử lý bên trong để giảm độ phức tạp của sơ đồ tổng thể.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Hướng dẫn cách xây dựng State Diagram cho đối tượng Order trong hệ thống thương mại điện tử."</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất các trạng thái phổ biến của Order gồm Created, Pending Payment, Paid, Shipping, Completed và Cancelled. Mỗi transition được kích hoạt bởi event tương ứng như paymentSuccess hoặc cancelOrder. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi áp dụng mô hình lifecycle này để thiết kế State Diagram cho Order, giúp kiểm tra tính hợp lệ của các trạng thái trong quá trình phát triển API.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Trong Activity Diagram, sự khác nhau giữa Control Flow và Object Flow là gì?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích Control Flow thể hiện thứ tự thực thi các hành động, trong khi Object Flow thể hiện sự di chuyển của dữ liệu hoặc object giữa các hoạt động. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi sử dụng Control Flow cho các quy trình xử lý thông thường và bổ sung Object Flow khi cần mô tả dữ liệu được truyền giữa các bước.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Làm thế nào để biểu diễn hoạt động song song trong Activity Diagram bằng PlantUML?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI hướng dẫn sử dụng cú pháp fork/join trong PlantUML để mô tả nhiều activity được thực hiện đồng thời. Ví dụ sau khi đặt hàng có thể thực hiện lưu Order và gửi Email Notification song song. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi áp dụng fork/join trong các Activity Diagram có xử lý bất đồng bộ để phản ánh chính xác kiến trúc hệ thống.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Activity Diagram có thể dùng để mô tả Use Case Detail không? Nếu có thì cần chú ý điều gì?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI cho rằng Activity Diagram phù hợp để mở rộng mô tả Use Case bằng cách thể hiện từng bước xử lý, điều kiện và vai trò tham gia. Tuy nhiên không nên mô tả quá sâu về code implementation. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi sử dụng Activity Diagram để bổ sung chi tiết cho các Use Case quan trọng nhưng vẫn giữ ở mức nghiệp vụ, tránh biến thành Flowchart của chương trình.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Khi một hệ thống có nhiều Actor tham gia, cách tổ chức Swimlane trong Activity Diagram như thế nào để tránh sơ đồ quá phức tạp?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất chỉ tạo Swimlane cho các Actor hoặc Module có trách nhiệm xử lý chính, không nên chia nhỏ mọi thành phần kỹ thuật. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi chỉ sử dụng các Swimlane quan trọng như Customer, Admin và System để giữ sơ đồ dễ đọc nhưng vẫn thể hiện rõ trách nhiệm.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Có cần thể hiện Database hoặc API Service trong Activity Diagram không?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích rằng Activity Diagram tập trung vào workflow nghiệp vụ nên không bắt buộc thể hiện chi tiết Database hoặc API. Những thành phần kỹ thuật chỉ nên thêm khi ảnh hưởng đến luồng xử lý chính. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi loại bỏ các thành phần kỹ thuật không cần thiết khỏi Activity Diagram nghiệp vụ để biểu đồ tập trung vào hành động của người dùng và hệ thống.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Làm sao kiểm tra một State Diagram có thiết kế đúng với business rule của hệ thống hay chưa?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI hướng dẫn kiểm tra bằng cách đối chiếu từng transition với nghiệp vụ thực tế, đảm bảo mỗi state có điều kiện chuyển hợp lệ và không tồn tại trạng thái không thể xảy ra. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi sử dụng business rule làm tiêu chí kiểm tra State Diagram thay vì chỉ dựa trên cấu trúc UML, giúp sơ đồ phản ánh đúng hệ thống thực tế.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Hướng dẫn kết hợp State Diagram và Activity Diagram trong tài liệu phân tích thiết kế phần mềm."</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích State Diagram mô tả vòng đời của một object cụ thể, còn Activity Diagram mô tả quy trình có sự tham gia của nhiều thành phần. Hai loại biểu đồ bổ trợ nhau trong việc phân tích hệ thống. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi sử dụng State Diagram cho các Entity quan trọng như Order, Payment và Activity Diagram cho các Use Case lớn nhằm tạo tài liệu thiết kế đầy đủ hơn.</t>
     </r>
   </si>
 </sst>
@@ -1617,30 +2693,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1648,18 +2724,410 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.5" customWidth="1"/>
+    <col min="3" max="3" width="37.5" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="128" x14ac:dyDescent="0.2">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="96" x14ac:dyDescent="0.2">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="96" x14ac:dyDescent="0.2">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="96" x14ac:dyDescent="0.2">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="96" x14ac:dyDescent="0.2">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="96" x14ac:dyDescent="0.2">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="96" x14ac:dyDescent="0.2">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" customWidth="1"/>
+    <col min="4" max="4" width="57.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="96" x14ac:dyDescent="0.2">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="81" x14ac:dyDescent="0.2">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="81" x14ac:dyDescent="0.2">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFB01A0E-1F98-F14C-89F4-16C22C80D1A6}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="31.6640625" customWidth="1"/>
+    <col min="4" max="4" width="58" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="96" x14ac:dyDescent="0.2">
+      <c r="A2" s="9">
+        <v>11</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A3" s="9">
+        <v>12</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A4" s="9">
+        <v>13</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A5" s="9">
+        <v>14</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A6" s="9">
+        <v>15</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A7" s="9">
+        <v>16</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="A8" s="9">
+        <v>17</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A9" s="9">
+        <v>18</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A10" s="9">
+        <v>19</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A11" s="9">
+        <v>20</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>